--- a/IEEE 39-bus System and a 3-terminal HVDC Grid/Input/DC_Lines.xlsx
+++ b/IEEE 39-bus System and a 3-terminal HVDC Grid/Input/DC_Lines.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pnnl-my.sharepoint.com/personal/quan_nguyen_pnnl_gov/Documents/Projects/NTP_HVDC/Models/ac_HVDC/Scenario 2/Scenario_2_shared with Siemens/Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pnnl-my.sharepoint.com/personal/quan_nguyen_pnnl_gov/Documents/Projects/NTP_HVDC/Models/ac_HVDC/Scenario 2/OAJPE_case/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="11_903AF6679E3AF0019C279CB362C0DF47093EDE3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FD360B3-9AAC-485D-96F2-A4E91F3829B5}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_903AF6679E3AF0019C279CB362C0DF47093EDE3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CB2C330-D138-4795-994D-E2A4354036E9}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-9347" windowWidth="16637" windowHeight="8983" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-9347" windowWidth="16637" windowHeight="8717" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IEEE13bus_AC_Lines" sheetId="1" r:id="rId1"/>
@@ -540,9 +540,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
@@ -868,20 +866,19 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="18.1015625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="8.83984375" style="2"/>
+    <col min="1" max="1" width="18.1015625" customWidth="1"/>
     <col min="4" max="4" width="15.41796875" customWidth="1"/>
     <col min="7" max="7" width="11.68359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
@@ -898,41 +895,37 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="G2">
-        <f>10.4/(46946.8/100)</f>
-        <v>2.2152734584678827E-2</v>
+        <v>4.718E-3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="2">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="2">
-        <f>10.4/(46946.8/100)</f>
-        <v>2.2152734584678827E-2</v>
+      <c r="G3">
+        <v>4.718E-3</v>
       </c>
     </row>
   </sheetData>
@@ -941,15 +934,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010069F3F1F7A7D2FC4CA657DAC3B87E2E2A" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f1920a2048c0da0dcd9f2bfb1e8a0e85">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4c12661f-3b4a-4dfc-9658-05dd562d81bb" xmlns:ns3="17291d1c-28a8-4f8b-8ad7-00352452765a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="373dfacf59998c13627043e9274e4d46" ns2:_="" ns3:_="">
     <xsd:import namespace="4c12661f-3b4a-4dfc-9658-05dd562d81bb"/>
@@ -1150,15 +1134,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A4C9DC0-EE8B-456C-B5CF-FC49E6362E33}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80D12152-48DA-4B44-BE14-08D0A0CD4CCF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1175,4 +1160,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A4C9DC0-EE8B-456C-B5CF-FC49E6362E33}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>